--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98271</v>
+        <v>98419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98271</v>
+        <v>98419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98271</v>
+        <v>98419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98419</v>
+        <v>98424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>98424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98419</v>
+        <v>98424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98424</v>
+        <v>98426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98424</v>
+        <v>98426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98424</v>
+        <v>98426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98426</v>
+        <v>98432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98426</v>
+        <v>98432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98426</v>
+        <v>98432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98432</v>
+        <v>98434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98432</v>
+        <v>98434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98432</v>
+        <v>98434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98434</v>
+        <v>98435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98434</v>
+        <v>98435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98434</v>
+        <v>98435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98435</v>
+        <v>98441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98435</v>
+        <v>98441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98435</v>
+        <v>98441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98441</v>
+        <v>98445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98441</v>
+        <v>98445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98441</v>
+        <v>98445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98445</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98449</v>
+        <v>98462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98449</v>
+        <v>98462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98449</v>
+        <v>98462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98462</v>
+        <v>98464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98462</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98462</v>
+        <v>98464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -718,11 +718,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -842,11 +838,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -966,11 +958,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98464</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98464</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36514-2025 artfynd.xlsx
+++ b/artfynd/A 36514-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134314909</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>134315051</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>134315058</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
